--- a/saida_pipeline/canal_endemico.xlsx
+++ b/saida_pipeline/canal_endemico.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M273"/>
+  <dimension ref="A1:Q273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,26 @@
           <t>razao_vs_p50</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>exames_marcador</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>positivos_marcador</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>numerador</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -529,10 +549,18 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -582,6 +610,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -621,6 +657,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -666,10 +710,18 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -709,6 +761,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -758,6 +818,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -807,6 +875,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -856,6 +932,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -901,10 +985,18 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -954,6 +1046,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -999,10 +1099,18 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1042,6 +1150,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1081,6 +1197,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1132,6 +1256,14 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1177,10 +1309,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1216,10 +1364,26 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1259,6 +1423,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1298,6 +1470,14 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1337,6 +1517,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1376,6 +1564,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1415,6 +1611,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1454,6 +1658,14 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1499,11 +1711,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1554,6 +1774,14 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1599,10 +1827,26 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1648,10 +1892,26 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1697,10 +1957,26 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1736,10 +2012,26 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1785,10 +2077,26 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1824,10 +2132,26 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1877,6 +2201,14 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1916,6 +2248,14 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1955,6 +2295,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1994,6 +2342,14 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2018,7 +2374,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
@@ -2039,10 +2395,26 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2082,6 +2454,14 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2121,6 +2501,14 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2156,10 +2544,26 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2205,10 +2609,26 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2258,6 +2678,14 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2282,7 +2710,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -2303,10 +2731,26 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2346,6 +2790,14 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2370,7 +2822,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2381,10 +2833,26 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2424,6 +2892,14 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2463,6 +2939,14 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2487,7 +2971,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -2508,10 +2992,26 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>35</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2551,6 +3051,14 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2600,6 +3108,14 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2645,10 +3161,26 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2694,10 +3226,18 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2747,6 +3287,14 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2796,6 +3344,14 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2845,6 +3401,14 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2894,6 +3458,14 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2943,6 +3515,14 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2992,6 +3572,14 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3016,7 +3604,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -3037,10 +3625,26 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3080,6 +3684,14 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3119,6 +3731,14 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3168,6 +3788,14 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3207,6 +3835,14 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3231,7 +3867,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>3</v>
@@ -3252,11 +3888,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>sucesso</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3297,6 +3947,14 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3336,6 +3994,14 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3381,11 +4047,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>sucesso</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -3436,6 +4116,14 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3485,6 +4173,14 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3524,6 +4220,14 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3563,6 +4267,14 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3602,6 +4314,14 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3647,11 +4367,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M72" t="n">
         <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -3692,6 +4420,14 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3741,6 +4477,14 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3786,10 +4530,26 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3814,7 +4574,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -3835,11 +4595,25 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>sucesso</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>16</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -3890,6 +4664,14 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3935,10 +4717,26 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3978,6 +4776,14 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4013,10 +4819,26 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4041,7 +4863,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
         <v>5</v>
@@ -4062,11 +4884,25 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>epidemia</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>3</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>21</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>IgM+PCR_arbovirose</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4113,10 +4949,26 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4156,6 +5008,14 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4195,6 +5055,14 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4230,10 +5098,26 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>16</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4269,10 +5153,26 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>679</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4312,6 +5212,14 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4351,6 +5259,14 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4390,6 +5306,14 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4429,6 +5353,14 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4468,6 +5400,14 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4507,6 +5447,14 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4546,6 +5494,14 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4585,6 +5541,14 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4624,6 +5588,14 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4663,6 +5635,14 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4712,6 +5692,14 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4751,6 +5739,14 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4790,6 +5786,14 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4829,6 +5833,14 @@
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4868,6 +5880,14 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4907,6 +5927,14 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4946,6 +5974,14 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4970,7 +6006,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4981,10 +6017,26 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5009,7 +6061,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -5030,10 +6082,26 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" t="n">
+        <v>2</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>HBV_DNA+HBsAg+anti_HBc_IgM</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5069,10 +6137,26 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5097,7 +6181,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -5108,10 +6192,26 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>4</v>
+      </c>
+      <c r="O107" t="n">
+        <v>2</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>HBV_DNA+HBsAg+anti_HBc_IgM</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5136,7 +6236,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>2</v>
@@ -5157,10 +6257,26 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5185,7 +6301,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -5206,10 +6322,26 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5255,10 +6387,26 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5283,7 +6431,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>2</v>
@@ -5304,10 +6452,26 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5332,7 +6496,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
         <v>4</v>
@@ -5353,11 +6517,25 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>epidemia</t>
-        </is>
-      </c>
-      <c r="M112" t="n">
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
         <v>4</v>
+      </c>
+      <c r="O112" t="n">
+        <v>3</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -5383,7 +6561,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>2</v>
@@ -5404,10 +6582,26 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5432,7 +6626,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G114" t="n">
         <v>5</v>
@@ -5457,7 +6651,23 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>7</v>
+        <v>3.6667</v>
+      </c>
+      <c r="N114" t="n">
+        <v>21</v>
+      </c>
+      <c r="O114" t="n">
+        <v>11</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -5483,31 +6693,47 @@
         </is>
       </c>
       <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
         <v>2</v>
       </c>
-      <c r="G115" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" t="n">
-        <v>1</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>sem_dado</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5532,7 +6758,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>2</v>
@@ -5553,10 +6779,26 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>HBV_DNA+HBsAg+anti_HBc_IgM</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5581,7 +6823,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>2</v>
@@ -5602,10 +6844,26 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5641,10 +6899,26 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5669,7 +6943,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G119" t="n">
         <v>3</v>
@@ -5690,11 +6964,27 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="M119" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>22</v>
+      </c>
+      <c r="O119" t="n">
+        <v>8</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>HBV_DNA+HBsAg+anti_HBc_IgM</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -5720,7 +7010,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -5745,6 +7035,22 @@
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>11</v>
+      </c>
+      <c r="O120" t="n">
+        <v>8</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5769,7 +7075,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5780,10 +7086,26 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>3</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5819,10 +7141,26 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5847,7 +7185,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -5868,10 +7206,26 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5896,7 +7250,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>2</v>
@@ -5917,10 +7271,26 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5945,7 +7315,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -5956,10 +7326,26 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>6</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5995,10 +7381,26 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6044,10 +7446,26 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6072,7 +7490,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -6093,10 +7511,26 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6142,10 +7576,26 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6170,7 +7620,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>5</v>
@@ -6191,11 +7641,25 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>seguranca</t>
-        </is>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>4</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -6221,7 +7685,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G131" t="n">
         <v>4</v>
@@ -6246,7 +7710,23 @@
         </is>
       </c>
       <c r="M131" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N131" t="n">
+        <v>13</v>
+      </c>
+      <c r="O131" t="n">
+        <v>7</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -6272,7 +7752,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
         <v>2</v>
@@ -6293,10 +7773,26 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6332,10 +7828,26 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
+        <v>3</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6381,11 +7893,25 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>seguranca</t>
-        </is>
-      </c>
-      <c r="M134" t="n">
-        <v>0.6667</v>
+          <t>volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>HBV_DNA</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -6436,6 +7962,14 @@
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6471,10 +8005,26 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6510,10 +8060,26 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6549,10 +8115,26 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6598,10 +8180,26 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>3</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6626,7 +8224,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -6637,10 +8235,26 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="n">
+        <v>2</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6676,10 +8290,26 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6725,10 +8355,26 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6774,10 +8420,26 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6802,7 +8464,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>2</v>
@@ -6823,10 +8485,26 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>HCV_RNA</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6866,6 +8544,14 @@
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6915,6 +8601,14 @@
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6954,6 +8648,14 @@
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6993,6 +8695,14 @@
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7032,6 +8742,14 @@
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7077,10 +8795,18 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>epidemia</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7120,6 +8846,14 @@
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7159,6 +8893,14 @@
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7198,6 +8940,14 @@
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7237,6 +8987,14 @@
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7286,6 +9044,14 @@
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7325,6 +9091,14 @@
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7360,10 +9134,26 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7388,7 +9178,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>2</v>
@@ -7409,10 +9199,26 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7458,10 +9264,26 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>4</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7501,6 +9323,14 @@
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7536,10 +9366,26 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7575,10 +9421,26 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7614,10 +9476,26 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7653,10 +9531,26 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7702,10 +9596,26 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7741,10 +9651,26 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7780,10 +9706,26 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7819,10 +9761,26 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7858,10 +9816,26 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>PCR_cultura_LCR</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7911,6 +9885,14 @@
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7950,6 +9932,14 @@
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7989,6 +9979,14 @@
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8028,6 +10026,14 @@
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8067,6 +10073,14 @@
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8106,6 +10120,14 @@
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8141,10 +10163,26 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
+      <c r="N176" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8180,10 +10218,26 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
+      <c r="N177" t="n">
+        <v>93</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8219,10 +10273,26 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
+      <c r="N178" t="n">
+        <v>16</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8268,10 +10338,26 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
+      <c r="N179" t="n">
+        <v>118</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8307,10 +10393,26 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
+      <c r="N180" t="n">
+        <v>679</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8346,10 +10448,26 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
+      <c r="N181" t="n">
+        <v>8</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8385,10 +10503,26 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
+      <c r="N182" t="n">
+        <v>27</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8424,10 +10558,26 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
+      <c r="N183" t="n">
+        <v>9</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -8463,10 +10613,26 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
+      <c r="N184" t="n">
+        <v>71</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8502,10 +10668,26 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8551,10 +10733,26 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>408</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8594,6 +10792,14 @@
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8633,6 +10839,14 @@
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -8668,10 +10882,26 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
+      <c r="N189" t="n">
+        <v>408</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>molecular</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8721,6 +10951,14 @@
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8766,11 +11004,19 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M191" t="n">
         <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -8821,6 +11067,14 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8866,11 +11120,19 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M193" t="n">
         <v>0</v>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -8911,6 +11173,14 @@
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8956,10 +11226,18 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9005,11 +11283,19 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M196" t="n">
         <v>0</v>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -9050,6 +11336,14 @@
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9089,6 +11383,14 @@
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9128,6 +11430,14 @@
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9167,6 +11477,14 @@
         </is>
       </c>
       <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9206,6 +11524,14 @@
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9255,6 +11581,14 @@
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9290,10 +11624,26 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9329,10 +11679,26 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9372,6 +11738,14 @@
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9411,6 +11785,14 @@
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -9456,10 +11838,26 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
+      <c r="N207" t="n">
+        <v>6</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -9499,6 +11897,14 @@
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -9538,6 +11944,14 @@
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9577,6 +11991,14 @@
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -9616,6 +12038,14 @@
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9655,6 +12085,14 @@
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9694,6 +12132,14 @@
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9733,6 +12179,14 @@
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9772,6 +12226,14 @@
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9811,6 +12273,14 @@
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9860,6 +12330,14 @@
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -9895,10 +12373,26 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M218" t="inlineStr"/>
+      <c r="N218" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -9934,10 +12428,26 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -9973,10 +12483,26 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M220" t="inlineStr"/>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10012,10 +12538,26 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M221" t="inlineStr"/>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10051,10 +12593,26 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M222" t="inlineStr"/>
+      <c r="N222" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" t="n">
+        <v>2</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10090,10 +12648,26 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M223" t="inlineStr"/>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10129,10 +12703,26 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -10178,10 +12768,26 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
+      <c r="N225" t="n">
+        <v>6</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10206,7 +12812,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -10217,10 +12823,26 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="n">
+        <v>1</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10266,10 +12888,26 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
+      <c r="N227" t="n">
+        <v>4</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>BAAR+TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10315,10 +12953,26 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10354,10 +13008,26 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="n">
+        <v>1</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10403,10 +13073,26 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M230" t="inlineStr"/>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10452,10 +13138,26 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
+      <c r="N231" t="n">
+        <v>4</v>
+      </c>
+      <c r="O231" t="n">
+        <v>4</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10480,7 +13182,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
         <v>2</v>
@@ -10501,10 +13203,26 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
+      <c r="N232" t="n">
+        <v>2</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10529,7 +13247,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G233" t="n">
         <v>2</v>
@@ -10550,10 +13268,26 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M233" t="inlineStr"/>
+      <c r="N233" t="n">
+        <v>3</v>
+      </c>
+      <c r="O233" t="n">
+        <v>3</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10599,10 +13333,26 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="n">
+        <v>1</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>LF_LAM</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10648,10 +13398,26 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
+      <c r="N235" t="n">
+        <v>4</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10697,10 +13463,26 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
+      <c r="N236" t="n">
+        <v>12</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10736,10 +13518,26 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
+      <c r="N237" t="n">
+        <v>2</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>BAAR+TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10775,10 +13573,26 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
+      <c r="N238" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10824,10 +13638,26 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
+      <c r="N239" t="n">
+        <v>2</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1</v>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>BAAR+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10852,7 +13682,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
         <v>2</v>
@@ -10873,10 +13703,26 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M240" t="inlineStr"/>
+      <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10912,10 +13758,26 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M241" t="inlineStr"/>
+      <c r="N241" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -10961,10 +13823,26 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M242" t="inlineStr"/>
+      <c r="N242" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -10989,7 +13867,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G243" t="n">
         <v>2</v>
@@ -11014,6 +13892,22 @@
         </is>
       </c>
       <c r="M243" t="inlineStr"/>
+      <c r="N243" t="n">
+        <v>65</v>
+      </c>
+      <c r="O243" t="n">
+        <v>11</v>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>BAAR+LF_LAM+TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -11059,10 +13953,26 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M244" t="inlineStr"/>
+      <c r="N244" t="n">
+        <v>2</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11108,10 +14018,26 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M245" t="inlineStr"/>
+      <c r="N245" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -11157,10 +14083,26 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M246" t="inlineStr"/>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11185,7 +14127,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -11196,10 +14138,26 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M247" t="inlineStr"/>
+      <c r="N247" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>1</v>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11245,10 +14203,26 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M248" t="inlineStr"/>
+      <c r="N248" t="n">
+        <v>4</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -11294,10 +14268,26 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M249" t="inlineStr"/>
+      <c r="N249" t="n">
+        <v>1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11333,10 +14323,26 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M250" t="inlineStr"/>
+      <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="n">
+        <v>2</v>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>BAAR</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -11376,6 +14382,14 @@
         </is>
       </c>
       <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11411,10 +14425,26 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M252" t="inlineStr"/>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11450,10 +14480,26 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M253" t="inlineStr"/>
+      <c r="N253" t="n">
+        <v>1</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>BAAR</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11478,7 +14524,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G254" t="n">
         <v>2</v>
@@ -11499,10 +14545,26 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M254" t="inlineStr"/>
+      <c r="N254" t="n">
+        <v>4</v>
+      </c>
+      <c r="O254" t="n">
+        <v>1</v>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11548,10 +14610,26 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M255" t="inlineStr"/>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11576,7 +14654,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -11587,10 +14665,26 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M256" t="inlineStr"/>
+      <c r="N256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11615,7 +14709,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -11626,10 +14720,26 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M257" t="inlineStr"/>
+      <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="n">
+        <v>1</v>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11675,10 +14785,26 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M258" t="inlineStr"/>
+      <c r="N258" t="n">
+        <v>2</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11724,10 +14850,26 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M259" t="inlineStr"/>
+      <c r="N259" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11752,7 +14894,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -11763,10 +14905,26 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M260" t="inlineStr"/>
+      <c r="N260" t="n">
+        <v>2</v>
+      </c>
+      <c r="O260" t="n">
+        <v>2</v>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11812,10 +14970,26 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M261" t="inlineStr"/>
+      <c r="N261" t="n">
+        <v>2</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11840,7 +15014,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G262" t="n">
         <v>2</v>
@@ -11861,10 +15035,26 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M262" t="inlineStr"/>
+      <c r="N262" t="n">
+        <v>8</v>
+      </c>
+      <c r="O262" t="n">
+        <v>2</v>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -11910,10 +15100,26 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M263" t="inlineStr"/>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>BAAR</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -11959,10 +15165,26 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M264" t="inlineStr"/>
+      <c r="N264" t="n">
+        <v>2</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -12012,6 +15234,14 @@
         </is>
       </c>
       <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -12047,10 +15277,26 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M266" t="inlineStr"/>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -12075,7 +15321,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G267" t="n">
         <v>2</v>
@@ -12096,10 +15342,26 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M267" t="inlineStr"/>
+      <c r="N267" t="n">
+        <v>12</v>
+      </c>
+      <c r="O267" t="n">
+        <v>2</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>BAAR+TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -12124,7 +15386,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" t="n">
         <v>2</v>
@@ -12145,10 +15407,26 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M268" t="inlineStr"/>
+      <c r="N268" t="n">
+        <v>6</v>
+      </c>
+      <c r="O268" t="n">
+        <v>1</v>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>BAAR+TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -12194,10 +15472,26 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M269" t="inlineStr"/>
+      <c r="N269" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>TRM_TB</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -12222,7 +15516,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G270" t="n">
         <v>2</v>
@@ -12243,10 +15537,26 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>sem_dado</t>
+          <t>volume_insuficiente</t>
         </is>
       </c>
       <c r="M270" t="inlineStr"/>
+      <c r="N270" t="n">
+        <v>37</v>
+      </c>
+      <c r="O270" t="n">
+        <v>4</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>BAAR+TRM_TB+cultura_TB</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>marcador_alerta</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -12292,11 +15602,19 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>seguranca</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M271" t="n">
         <v>0</v>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -12337,6 +15655,14 @@
         </is>
       </c>
       <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -12382,10 +15708,18 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>sucesso</t>
         </is>
       </c>
       <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>positivos_semanais_brutos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40690,7 +44024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40912,60 +44246,96 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zona_count_alerta</t>
+          <t>filtro_marcadores</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Numerador da SE atual = positivos com conta_bortman (regras_agravo_gal); IgG/anti-HBs fora. n_mínimo=5 para zona epidêmica. Zona 'epidemia' = classificação estatística (P75), não declaração epidemiológica.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zona_count_epidemia</t>
+          <t>n_minimo_marcador</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zona_count_seguranca</t>
+          <t>terminologia_zona_epidemia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>zona epidêmica (estatística)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zona_count_sem_dado</t>
+          <t>zona_count_alerta</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>zona_count_epidemia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>zona_count_sem_dado</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>zona_count_sucesso</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>zona_count_volume_insuficiente</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
     </row>
